--- a/WorkBot/main/data/order_archive/W.B. Mason Co., Inc/W.B. Mason Co., Inc_Downtown_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/W.B. Mason Co., Inc/W.B. Mason Co., Inc_Downtown_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,6 +521,48 @@
         <v>72.73999999999999</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HERX7658QK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Trash Bag (38x58)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CSICANTINA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bag Paper - Handle (Small)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
